--- a/public/downloads/HoffmannFramework2016.xlsx
+++ b/public/downloads/HoffmannFramework2016.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>CO</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CH</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>NO</t>
@@ -659,10 +682,10 @@
         <v>48</v>
       </c>
       <c r="N3" s="5">
-        <v>69.27185606956482</v>
+        <v>69271.85606956482</v>
       </c>
       <c r="O3" s="4">
-        <v>0.0344464724363823</v>
+        <v>34.4464724363823</v>
       </c>
       <c r="P3" s="5">
         <v>2011</v>
@@ -709,10 +732,10 @@
         <v>48</v>
       </c>
       <c r="N4" s="5">
-        <v>70.70943021774292</v>
+        <v>70709.43021774292</v>
       </c>
       <c r="O4" s="4">
-        <v>0.03311917106217467</v>
+        <v>33.11917106217467</v>
       </c>
       <c r="P4" s="5">
         <v>2135</v>
@@ -759,10 +782,10 @@
         <v>48</v>
       </c>
       <c r="N5" s="5">
-        <v>388.3483383655548</v>
+        <v>388348.3383655548</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1803754474526497</v>
+        <v>180.3754474526497</v>
       </c>
       <c r="P5" s="5">
         <v>2153</v>
@@ -809,10 +832,10 @@
         <v>48</v>
       </c>
       <c r="N6" s="5">
-        <v>162.118688583374</v>
+        <v>162118.688583374</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08408645673411516</v>
+        <v>84.08645673411516</v>
       </c>
       <c r="P6" s="5">
         <v>1928</v>
@@ -859,10 +882,10 @@
         <v>48</v>
       </c>
       <c r="N7" s="5">
-        <v>261.151401758194</v>
+        <v>261151.401758194</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1372314249911687</v>
+        <v>137.2314249911687</v>
       </c>
       <c r="P7" s="5">
         <v>1903</v>
@@ -909,10 +932,10 @@
         <v>48</v>
       </c>
       <c r="N8" s="5">
-        <v>17.78126621246338</v>
+        <v>17781.26621246338</v>
       </c>
       <c r="O8" s="4">
-        <v>0.00918928486432216</v>
+        <v>9.189284864322159</v>
       </c>
       <c r="P8" s="5">
         <v>1935</v>
@@ -959,10 +982,10 @@
         <v>48</v>
       </c>
       <c r="N9" s="5">
-        <v>59.30932211875916</v>
+        <v>59309.32211875916</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02820224542023735</v>
+        <v>28.20224542023735</v>
       </c>
       <c r="P9" s="5">
         <v>2103</v>
@@ -1009,10 +1032,10 @@
         <v>48</v>
       </c>
       <c r="N10" s="5">
-        <v>174.9959194660187</v>
+        <v>174995.9194660187</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08227358696098669</v>
+        <v>82.27358696098669</v>
       </c>
       <c r="P10" s="5">
         <v>2127</v>
@@ -1059,10 +1082,10 @@
         <v>48</v>
       </c>
       <c r="N11" s="5">
-        <v>80.28305339813232</v>
+        <v>80283.05339813232</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03716808027691311</v>
+        <v>37.16808027691311</v>
       </c>
       <c r="P11" s="5">
         <v>2160</v>
@@ -1109,10 +1132,10 @@
         <v>48</v>
       </c>
       <c r="N12" s="5">
-        <v>39.74710249900818</v>
+        <v>39747.10249900818</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01765753109684948</v>
+        <v>17.65753109684948</v>
       </c>
       <c r="P12" s="5">
         <v>2251</v>
@@ -1159,10 +1182,10 @@
         <v>48</v>
       </c>
       <c r="N13" s="5">
-        <v>150.9768691062927</v>
+        <v>150976.8691062927</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07314770790033562</v>
+        <v>73.14770790033562</v>
       </c>
       <c r="P13" s="5">
         <v>2064</v>
@@ -1209,10 +1232,10 @@
         <v>18</v>
       </c>
       <c r="N14" s="5">
-        <v>93.95252633094788</v>
+        <v>93952.52633094788</v>
       </c>
       <c r="O14" s="4">
-        <v>0.206036241953833</v>
+        <v>206.036241953833</v>
       </c>
       <c r="P14" s="5">
         <v>456</v>
@@ -1259,10 +1282,10 @@
         <v>18</v>
       </c>
       <c r="N15" s="5">
-        <v>204.6104426383972</v>
+        <v>204610.4426383972</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2066772147862598</v>
+        <v>206.6772147862598</v>
       </c>
       <c r="P15" s="5">
         <v>990</v>
@@ -1309,10 +1332,10 @@
         <v>18</v>
       </c>
       <c r="N16" s="5">
-        <v>52.84985446929932</v>
+        <v>52849.85446929932</v>
       </c>
       <c r="O16" s="4">
-        <v>0.0989697649237815</v>
+        <v>98.9697649237815</v>
       </c>
       <c r="P16" s="5">
         <v>534</v>
@@ -1359,10 +1382,10 @@
         <v>18</v>
       </c>
       <c r="N17" s="5">
-        <v>99.30272936820984</v>
+        <v>99302.72936820984</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1006106680528975</v>
+        <v>100.6106680528975</v>
       </c>
       <c r="P17" s="5">
         <v>987</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,25 +1497,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1324286142566631</v>
+        <v>0.5909092714032197</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1324286142566631</v>
+        <v>0.5909092714032197</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1319852123976488</v>
+        <v>0.5863480163512415</v>
       </c>
       <c r="E3" s="4">
-        <v>86.80272108843538</v>
+        <v>91.53061224489795</v>
       </c>
       <c r="F3" s="4">
-        <v>93.69686800894856</v>
+        <v>96.03467561521254</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1501,25 +1556,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5909092714032197</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05485711424599752</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05485711424599752</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.06556188383346055</v>
+        <v>0.4109194356573038</v>
       </c>
       <c r="C4" s="4">
-        <v>0.06556188383346055</v>
+        <v>0.4109194356573038</v>
       </c>
       <c r="D4" s="4">
-        <v>0.05964626507170859</v>
+        <v>0.3968326237157097</v>
       </c>
       <c r="E4" s="4">
-        <v>84.0873015873016</v>
+        <v>88.19727891156464</v>
       </c>
       <c r="F4" s="4">
-        <v>92.95302013422818</v>
+        <v>94.50223713646533</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -1542,34 +1615,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4060445625249796</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1687494867606548</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1687494867606548</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.08791265973561989</v>
+        <v>0.1191931248160433</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1027950282224837</v>
+        <v>0.1191931248160433</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1003090929946968</v>
+        <v>0.1219514411600959</v>
       </c>
       <c r="E5" s="4">
-        <v>81.11678004535167</v>
+        <v>87.46598639455782</v>
       </c>
       <c r="F5" s="4">
-        <v>90.45302013422796</v>
+        <v>93.88702460850111</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.02167449702971996</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1191931248160433</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1191931248160433</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,25 +1797,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1492342303819993</v>
+        <v>0.2604391240815234</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1492342303819993</v>
+        <v>0.2604391240815234</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1376221329597174</v>
+        <v>0.266744182878724</v>
       </c>
       <c r="E3" s="4">
-        <v>86.75170068027209</v>
+        <v>89.30272108843531</v>
       </c>
       <c r="F3" s="4">
-        <v>93.6856823266219</v>
+        <v>94.61968680089483</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1714,25 +1856,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2604391240815234</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09707919852392892</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09707919852392892</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9475803835928353</v>
+        <v>0.3023011834052741</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9475803835928353</v>
+        <v>0.3023011834052741</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9546278778453581</v>
+        <v>0.2797426663604792</v>
       </c>
       <c r="E4" s="4">
-        <v>90.1530612244898</v>
+        <v>89.96598639455783</v>
       </c>
       <c r="F4" s="4">
-        <v>95.39709172259509</v>
+        <v>94.13310961968681</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -1755,25 +1915,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2345966242571556</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3291059145557869</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3291059145557869</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1753919105525827</v>
+        <v>0.5100448387263276</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1753919105525827</v>
+        <v>0.5100448387263276</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1900381228125111</v>
+        <v>0.4514692085383392</v>
       </c>
       <c r="E5" s="4">
-        <v>86.54761904761901</v>
+        <v>85.17006802721085</v>
       </c>
       <c r="F5" s="4">
-        <v>92.53914988814329</v>
+        <v>92.08612975391506</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -1796,9 +1974,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2868308054640397</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5232164416090569</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5232164416090569</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2097,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2023365502774714</v>
+        <v>0.06556188383346055</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2023365502774714</v>
+        <v>0.06556188383346055</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2066363498787084</v>
+        <v>0.05964626507170859</v>
       </c>
       <c r="E3" s="4">
-        <v>84.66553287981856</v>
+        <v>84.0873015873016</v>
       </c>
       <c r="F3" s="4">
-        <v>92.57084265473527</v>
+        <v>92.95302013422818</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1927,25 +2156,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02516828188044018</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04878302924650043</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04878302924650043</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4055539306263216</v>
+        <v>0.1324286142566631</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4055539306263216</v>
+        <v>0.1324286142566631</v>
       </c>
       <c r="D4" s="4">
-        <v>0.411539508527526</v>
+        <v>0.1319852123976488</v>
       </c>
       <c r="E4" s="4">
-        <v>83.84920634920634</v>
+        <v>86.80272108843538</v>
       </c>
       <c r="F4" s="4">
-        <v>92.70320656226694</v>
+        <v>93.69686800894856</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -1968,34 +2215,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1303865561823707</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06732492240542721</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06732492240542721</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1389961276920273</v>
+        <v>0.08791265973561989</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1389961276920273</v>
+        <v>0.1027950282224837</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1278718346825872</v>
+        <v>0.1003090929946968</v>
       </c>
       <c r="E5" s="4">
-        <v>77.83446712018142</v>
+        <v>81.11678004535167</v>
       </c>
       <c r="F5" s="4">
-        <v>88.59992542878452</v>
+        <v>90.45302013422796</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2009,9 +2274,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.08464981930695632</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06779732118811922</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06172665810409167</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2397,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5776035790860651</v>
+        <v>0.9475803835928353</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5776035790860651</v>
+        <v>0.9475803835928353</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5675044859667617</v>
+        <v>0.9546278778453581</v>
       </c>
       <c r="E3" s="4">
-        <v>88.33333333333336</v>
+        <v>90.1530612244898</v>
       </c>
       <c r="F3" s="4">
-        <v>94.09955257270693</v>
+        <v>95.39709172259509</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2140,25 +2456,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.9475803835928353</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0976081757124632</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0976081757124632</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.05836184277591139</v>
+        <v>0.1492342303819993</v>
       </c>
       <c r="C4" s="4">
-        <v>0.05836184277591139</v>
+        <v>0.1492342303819993</v>
       </c>
       <c r="D4" s="4">
-        <v>0.05805396491743157</v>
+        <v>0.1376221329597174</v>
       </c>
       <c r="E4" s="4">
-        <v>90.40816326530613</v>
+        <v>86.75170068027209</v>
       </c>
       <c r="F4" s="4">
-        <v>95.5592841163311</v>
+        <v>93.6856823266219</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2181,25 +2515,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03537056275406315</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1374440427973116</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1374440427973116</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5631655680372819</v>
+        <v>0.1753919105525827</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5631655680372819</v>
+        <v>0.1753919105525827</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5342196451857194</v>
+        <v>0.1900381228125111</v>
       </c>
       <c r="E5" s="4">
-        <v>84.26870748299309</v>
+        <v>86.54761904761901</v>
       </c>
       <c r="F5" s="4">
-        <v>91.40939597315447</v>
+        <v>92.53914988814329</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.01247650655453449</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1795507460707608</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1795507460707608</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,25 +2697,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3649084401309606</v>
+        <v>0.4055539306263216</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3649084401309606</v>
+        <v>0.4055539306263216</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3642861999253548</v>
+        <v>0.411539508527526</v>
       </c>
       <c r="E3" s="4">
-        <v>97.60204081632654</v>
+        <v>83.84920634920634</v>
       </c>
       <c r="F3" s="4">
-        <v>98.71364653243849</v>
+        <v>92.70320656226694</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2353,25 +2756,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4055539306263216</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04325987619123698</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04325987619123698</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4197524374981791</v>
+        <v>0.2023365502774714</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4197524374981791</v>
+        <v>0.2023365502774714</v>
       </c>
       <c r="D4" s="4">
-        <v>0.423607745395111</v>
+        <v>0.2066363498787084</v>
       </c>
       <c r="E4" s="4">
-        <v>97.87414965986395</v>
+        <v>84.66553287981856</v>
       </c>
       <c r="F4" s="4">
-        <v>98.90939597315436</v>
+        <v>92.57084265473527</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2394,25 +2815,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1534947298784935</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1106671991965087</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1106671991965087</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1139746484393356</v>
+        <v>0.1389961276920273</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1139746484393356</v>
+        <v>0.1389961276920273</v>
       </c>
       <c r="D5" s="4">
-        <v>0.09388446581706184</v>
+        <v>0.1278718346825872</v>
       </c>
       <c r="E5" s="4">
-        <v>97.0748299319728</v>
+        <v>77.83446712018142</v>
       </c>
       <c r="F5" s="4">
-        <v>98.43959731543625</v>
+        <v>88.59992542878452</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2435,9 +2874,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.07874399694149738</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08650012973102907</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08650012973102907</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2997,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2164220417757833</v>
+        <v>0.05836184277591139</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2164220417757833</v>
+        <v>0.05836184277591139</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2052395945012574</v>
+        <v>0.05805396491743157</v>
       </c>
       <c r="E3" s="4">
-        <v>84.26870748299321</v>
+        <v>90.40816326530613</v>
       </c>
       <c r="F3" s="4">
-        <v>92.34899328859061</v>
+        <v>95.5592841163311</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2566,25 +3056,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.03109339239796875</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04824892642158855</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04824892642158855</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.501476559664817</v>
+        <v>0.5776035790860651</v>
       </c>
       <c r="C4" s="4">
-        <v>1.501476559664817</v>
+        <v>0.5776035790860651</v>
       </c>
       <c r="D4" s="4">
-        <v>1.502154736346017</v>
+        <v>0.5675044859667617</v>
       </c>
       <c r="E4" s="4">
-        <v>84.72789115646259</v>
+        <v>88.33333333333336</v>
       </c>
       <c r="F4" s="4">
-        <v>93.2829977628635</v>
+        <v>94.09955257270693</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2607,25 +3115,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.5384275657753034</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2186518685691962</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2186518685691962</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7569397168591122</v>
+        <v>0.5631655680372819</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7569397168591122</v>
+        <v>0.5631655680372819</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7362006979420287</v>
+        <v>0.5342196451857194</v>
       </c>
       <c r="E5" s="4">
-        <v>78.6904761904763</v>
+        <v>84.26870748299309</v>
       </c>
       <c r="F5" s="4">
-        <v>88.93736017897081</v>
+        <v>91.40939597315447</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5631655680372819</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1744848544105554</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1744848544105554</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3371807617128011</v>
+        <v>0.4197524374981791</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3371807617128011</v>
+        <v>0.4197524374981791</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3388452537040031</v>
+        <v>0.423607745395111</v>
       </c>
       <c r="E3" s="4">
-        <v>96.98979591836735</v>
+        <v>97.87414965986395</v>
       </c>
       <c r="F3" s="4">
-        <v>98.55145413870247</v>
+        <v>98.90939597315436</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2779,25 +3356,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4197524374981791</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04544291197167855</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04544291197167855</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4713908668617477</v>
+        <v>0.3649084401309606</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4713908668617477</v>
+        <v>0.3649084401309606</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4727193153162867</v>
+        <v>0.3642861999253548</v>
       </c>
       <c r="E4" s="4">
-        <v>97.90816326530613</v>
+        <v>97.60204081632654</v>
       </c>
       <c r="F4" s="4">
-        <v>98.69686800894856</v>
+        <v>98.71364653243849</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2820,34 +3415,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3649084401309606</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03673803565688352</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03673803565688352</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.0408515289132439</v>
+        <v>0.1139746484393356</v>
       </c>
       <c r="C5" s="4">
-        <v>0.0401279033525076</v>
+        <v>0.1139746484393356</v>
       </c>
       <c r="D5" s="4">
-        <v>0.05411080566094745</v>
+        <v>0.09388446581706184</v>
       </c>
       <c r="E5" s="4">
-        <v>89.23469387755078</v>
+        <v>97.0748299319728</v>
       </c>
       <c r="F5" s="4">
-        <v>90.32997762863705</v>
+        <v>98.43959731543625</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2861,9 +3474,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1139746484393356</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04721359490052759</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04721359490052759</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3597,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1024373327910904</v>
+        <v>1.501476559664817</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1024373327910904</v>
+        <v>1.501476559664817</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1008604894300306</v>
+        <v>1.502154736346017</v>
       </c>
       <c r="E3" s="4">
-        <v>85.54421768707483</v>
+        <v>84.72789115646259</v>
       </c>
       <c r="F3" s="4">
-        <v>93.14876957494408</v>
+        <v>93.2829977628635</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2992,25 +3656,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.501476559664817</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04958031432191682</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04958031432191682</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8462602482497803</v>
+        <v>0.2164220417757833</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8462602482497803</v>
+        <v>0.2164220417757833</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8529617474734894</v>
+        <v>0.2052395945012574</v>
       </c>
       <c r="E4" s="4">
-        <v>83.9965986394558</v>
+        <v>84.26870748299321</v>
       </c>
       <c r="F4" s="4">
-        <v>93.00335570469797</v>
+        <v>92.34899328859061</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -3033,25 +3715,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1399351773480453</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1231319235437531</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1231319235437531</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4771839307978255</v>
+        <v>0.7569397168591122</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4771839307978255</v>
+        <v>0.7569397168591122</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4624165075256926</v>
+        <v>0.7362006979420287</v>
       </c>
       <c r="E5" s="4">
-        <v>79.50680272108839</v>
+        <v>78.6904761904763</v>
       </c>
       <c r="F5" s="4">
-        <v>89.61968680089493</v>
+        <v>88.93736017897081</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.7569397168591122</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09717205619843629</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09717205619843629</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4713908668617477</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4713908668617477</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4727193153162867</v>
+      </c>
+      <c r="E3" s="4">
+        <v>97.90816326530613</v>
+      </c>
+      <c r="F3" s="4">
+        <v>98.69686800894856</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4713908668617477</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04511054384570631</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04511054384570631</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3371807617128011</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3371807617128011</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3388452537040031</v>
+      </c>
+      <c r="E4" s="4">
+        <v>96.98979591836735</v>
+      </c>
+      <c r="F4" s="4">
+        <v>98.55145413870247</v>
+      </c>
+      <c r="G4" s="5">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3371807617128011</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04921262521961251</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04921262521961251</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.0408515289132439</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.0401279033525076</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.05411080566094745</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.23469387755078</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.32997762863705</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.009606961113577905</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0408515289132439</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03820651112979202</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.8462602482497803</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.8462602482497803</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.8529617474734894</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.9965986394558</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.00335570469797</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.8462602482497803</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03587548292040976</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03587548292040976</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1024373327910904</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1024373327910904</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1008604894300306</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.54421768707483</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.14876957494408</v>
+      </c>
+      <c r="G4" s="5">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.01872713295816157</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0910719621357256</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0910719621357256</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4771839307978255</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4771839307978255</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4624165075256926</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.50680272108839</v>
+      </c>
+      <c r="F5" s="4">
+        <v>89.61968680089493</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4771839307978255</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07328577667295567</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07328577667295567</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>97.91666666666666</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1093992020995611</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1081634496209517</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.340910948098566</v>
+      </c>
+      <c r="K3" s="4">
+        <v>90.40462018140607</v>
+      </c>
+      <c r="L3" s="4">
+        <v>94.78001491424313</v>
+      </c>
+      <c r="M3" s="5">
+        <v>48</v>
+      </c>
+      <c r="N3" s="5">
+        <v>69271.85606956482</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.4464724363823</v>
+      </c>
+      <c r="P3" s="5">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1766896935727388</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1766896935727388</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.1753048599233669</v>
+      </c>
+      <c r="K4" s="4">
+        <v>87.2874149659864</v>
+      </c>
+      <c r="L4" s="4">
+        <v>93.32634228187915</v>
+      </c>
+      <c r="M4" s="5">
+        <v>48</v>
+      </c>
+      <c r="N4" s="5">
+        <v>70709.43021774292</v>
+      </c>
+      <c r="O4" s="4">
+        <v>33.11917106217467</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1057297623294504</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1057297623294504</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1035985767236474</v>
+      </c>
+      <c r="K5" s="4">
+        <v>88.02791950113378</v>
+      </c>
+      <c r="L5" s="4">
+        <v>94.27246457867263</v>
+      </c>
+      <c r="M5" s="5">
+        <v>48</v>
+      </c>
+      <c r="N5" s="5">
+        <v>388348.3383655548</v>
+      </c>
+      <c r="O5" s="4">
+        <v>180.3754474526497</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1562059893804407</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1562059893804407</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1709659077608982</v>
+      </c>
+      <c r="K6" s="4">
+        <v>90.6065759637187</v>
+      </c>
+      <c r="L6" s="4">
+        <v>95.05709358687544</v>
+      </c>
+      <c r="M6" s="5">
+        <v>48</v>
+      </c>
+      <c r="N6" s="5">
+        <v>162118.688583374</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.08645673411516</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.0632020804033967</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.0632020804033967</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.06256690272757783</v>
+      </c>
+      <c r="K7" s="4">
+        <v>88.82653061224492</v>
+      </c>
+      <c r="L7" s="4">
+        <v>94.73830164056673</v>
+      </c>
+      <c r="M7" s="5">
+        <v>48</v>
+      </c>
+      <c r="N7" s="5">
+        <v>261151.401758194</v>
+      </c>
+      <c r="O7" s="4">
+        <v>137.2314249911687</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.08377726185271246</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.08377726185271246</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.08310618196215616</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.19005102040816</v>
+      </c>
+      <c r="L8" s="4">
+        <v>94.8538870246085</v>
+      </c>
+      <c r="M8" s="5">
+        <v>48</v>
+      </c>
+      <c r="N8" s="5">
+        <v>17781.26621246338</v>
+      </c>
+      <c r="O8" s="4">
+        <v>9.189284864322159</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>100</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.2413469450194934</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2413469450194934</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2735281118474668</v>
+      </c>
+      <c r="K9" s="4">
+        <v>87.40433673469387</v>
+      </c>
+      <c r="L9" s="4">
+        <v>93.11404735272187</v>
+      </c>
+      <c r="M9" s="5">
+        <v>48</v>
+      </c>
+      <c r="N9" s="5">
+        <v>59309.32211875916</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.20224542023735</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>97.91666666666666</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.07100020764619557</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.07042253894487512</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.07284143392556704</v>
+      </c>
+      <c r="K10" s="4">
+        <v>83.74716553287961</v>
+      </c>
+      <c r="L10" s="4">
+        <v>92.19402498135742</v>
+      </c>
+      <c r="M10" s="5">
+        <v>48</v>
+      </c>
+      <c r="N10" s="5">
+        <v>174995.9194660187</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.27358696098669</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1019514894656189</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1019514894656189</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1023510620332965</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.10090702947848</v>
+      </c>
+      <c r="L11" s="4">
+        <v>94.09139634601037</v>
+      </c>
+      <c r="M11" s="5">
+        <v>48</v>
+      </c>
+      <c r="N11" s="5">
+        <v>80283.05339813232</v>
+      </c>
+      <c r="O11" s="4">
+        <v>37.16808027691311</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.07764009364271544</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.07764009364271544</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.07762861802033805</v>
+      </c>
+      <c r="K12" s="4">
+        <v>83.11295351473915</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.74613161819546</v>
+      </c>
+      <c r="M12" s="5">
+        <v>48</v>
+      </c>
+      <c r="N12" s="5">
+        <v>39747.10249900818</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.65753109684948</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1010090010107651</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1010090010107651</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.09988463780900891</v>
+      </c>
+      <c r="K13" s="4">
+        <v>88.70960884353747</v>
+      </c>
+      <c r="L13" s="4">
+        <v>94.24496644295296</v>
+      </c>
+      <c r="M13" s="5">
+        <v>48</v>
+      </c>
+      <c r="N13" s="5">
+        <v>150976.8691062927</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.14770790033562</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.04313151417636322</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.04313151417636322</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.04441280601185744</v>
+      </c>
+      <c r="K14" s="4">
+        <v>97.51700680272108</v>
+      </c>
+      <c r="L14" s="4">
+        <v>98.68754660700969</v>
+      </c>
+      <c r="M14" s="5">
+        <v>18</v>
+      </c>
+      <c r="N14" s="5">
+        <v>93952.52633094788</v>
+      </c>
+      <c r="O14" s="4">
+        <v>206.036241953833</v>
+      </c>
+      <c r="P14" s="5">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.08996143135470207</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.08996143135470207</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.09302231922912395</v>
+      </c>
+      <c r="K15" s="4">
+        <v>82.56235827664416</v>
+      </c>
+      <c r="L15" s="4">
+        <v>91.52311707680818</v>
+      </c>
+      <c r="M15" s="5">
+        <v>18</v>
+      </c>
+      <c r="N15" s="5">
+        <v>204610.4426383972</v>
+      </c>
+      <c r="O15" s="4">
+        <v>206.6772147862598</v>
+      </c>
+      <c r="P15" s="5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.0450582326595209</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.04452773941416899</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.04864793405145151</v>
+      </c>
+      <c r="K16" s="4">
+        <v>94.71088435374081</v>
+      </c>
+      <c r="L16" s="4">
+        <v>95.85943325875978</v>
+      </c>
+      <c r="M16" s="5">
+        <v>18</v>
+      </c>
+      <c r="N16" s="5">
+        <v>52849.85446929932</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.9697649237815</v>
+      </c>
+      <c r="P16" s="5">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.06674440724303035</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.06674440724303035</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.06415040006809859</v>
+      </c>
+      <c r="K17" s="4">
+        <v>83.01587301587317</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.92393736017883</v>
+      </c>
+      <c r="M17" s="5">
+        <v>18</v>
+      </c>
+      <c r="N17" s="5">
+        <v>99302.72936820984</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.6106680528975</v>
+      </c>
+      <c r="P17" s="5">
+        <v>987</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>47</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>48</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>48</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>48</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>48</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>48</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>48</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>47</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>48</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>48</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,78 +6864,112 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>26.34463893734019</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.4390348927438346</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.08276643990931</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.02050708426547</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>6</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-26.34463893734019</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05685744540254589</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05685744540254589</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.6525561554054303</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.6525561554054303</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.6371085388282819</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>92.38662131519276</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>95.77554064131243</v>
       </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>26.34463893734019</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4390348927438346</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.08276643990931</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.02050708426547</v>
-      </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -3999,12 +6978,30 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.6525561554054303</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2000194566124091</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2000194566124091</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.16743285235078</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.01039432655013435</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1708976278674914</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1715812397221488</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,67 +7162,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>1.165336178117982</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.165336178117982</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.168464865658672</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.66326530612245</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.38851603281132</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.165336178117982</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2080985183099349</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2080985183099349</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.3508730473935489</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.3508730473935489</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.3551985962013288</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>85.78798185941042</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>93.12826249067859</v>
       </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.165336178117982</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.165336178117982</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.168464865658672</v>
-      </c>
-      <c r="E4" s="4">
-        <v>90.66326530612245</v>
-      </c>
-      <c r="F4" s="4">
-        <v>94.38851603281132</v>
-      </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
@@ -4214,10 +7280,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3508730473935489</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1974586661869109</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1974586661869109</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1609860676708913</v>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.04014132690772459</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.149069531868847</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.149069531868847</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,67 +7462,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.3267947794258682</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3267947794258682</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3351847664773551</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.62131519274377</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.98396718866519</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3267947794258682</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.038875354791254</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.038875354791254</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.227534787627061</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.227534787627061</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.2260111910820005</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>87.94217687074831</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>94.30089485458613</v>
       </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3267947794258682</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3267947794258682</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3351847664773551</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.62131519274377</v>
-      </c>
-      <c r="F4" s="4">
-        <v>93.98396718866519</v>
-      </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1615394756515705</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1378536588928585</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1378536588928585</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3131352596971593</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.0861797421906893</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2844086789669296</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2844086789669296</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,67 +7762,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.2326095438261914</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2326095438261914</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.214270704613138</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.67687074829934</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.13982102908278</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2326095438261914</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0698547761340168</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0698547761340168</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.186358690780401</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.186358690780401</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.1595102300869961</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>94.31972789115648</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>96.77293064876955</v>
       </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2326095438261914</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2326095438261914</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.214270704613138</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.67687074829934</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.13982102908278</v>
-      </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08759933142064842</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1522510021614609</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1522510021614609</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1312081758453893</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.05397739283586587</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1312081758453893</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1312081758453893</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,67 +8062,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.1037064059317025</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1037064059317025</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1038974586864225</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.11904761904762</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.67114093959732</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1037064059317025</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05219885440709312</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05219885440709312</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.181137800735235</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.181137800735235</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.1774226034899551</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>89.13265306122449</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>94.83780760626399</v>
       </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1037064059317025</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1037064059317025</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1038974586864225</v>
-      </c>
-      <c r="E4" s="4">
-        <v>90.11904761904762</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.67114093959732</v>
-      </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.07581525472997461</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1305942975819186</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1305942975819186</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1555976901920273</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1246789919569596</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07247836222072089</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07247836222072089</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4109194356573038</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4109194356573038</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3968326237157097</v>
-      </c>
-      <c r="E3" s="4">
-        <v>88.19727891156464</v>
-      </c>
-      <c r="F3" s="4">
-        <v>94.50223713646533</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5909092714032197</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5909092714032197</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5863480163512415</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.53061224489795</v>
-      </c>
-      <c r="F4" s="4">
-        <v>96.03467561521254</v>
-      </c>
-      <c r="G4" s="5">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1191931248160433</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1191931248160433</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1219514411600959</v>
-      </c>
-      <c r="E5" s="4">
-        <v>87.46598639455782</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.88702460850111</v>
-      </c>
-      <c r="G5" s="5">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3023011834052741</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3023011834052741</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2797426663604792</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.96598639455783</v>
-      </c>
-      <c r="F3" s="4">
-        <v>94.13310961968681</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2604391240815234</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2604391240815234</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.266744182878724</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.30272108843531</v>
-      </c>
-      <c r="F4" s="4">
-        <v>94.61968680089483</v>
-      </c>
-      <c r="G4" s="5">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5100448387263276</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5100448387263276</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4514692085383392</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.17006802721085</v>
-      </c>
-      <c r="F5" s="4">
-        <v>92.08612975391506</v>
-      </c>
-      <c r="G5" s="5">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/HoffmannFramework2016.xlsx
+++ b/public/downloads/HoffmannFramework2016.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5909092714032197</v>
+        <v>0.5601483557855342</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05485711424599752</v>
+        <v>0.04789073276836146</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05485711424599752</v>
+        <v>0.04789073276836146</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4060445625249796</v>
+        <v>-0.4482261664744784</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.02167449702971996</v>
+        <v>-0.02059590127231287</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2604391240815234</v>
+        <v>0.2604749201442385</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2345966242571556</v>
+        <v>-0.07709121540280856</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3291059145557869</v>
+        <v>0.291223156727097</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3291059145557869</v>
+        <v>0.291223156727097</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2868308054640397</v>
+        <v>-0.1236579984079257</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5232164416090569</v>
+        <v>0.4869721227804447</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5232164416090569</v>
+        <v>0.4869721227804447</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02516828188044018</v>
+        <v>-0.03611401961598837</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04878302924650043</v>
+        <v>0.04604313377462358</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04878302924650043</v>
+        <v>0.04604313377462358</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1303865561823707</v>
+        <v>0.1313391925345456</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06732492240542721</v>
+        <v>0.06732492240542723</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06732492240542721</v>
+        <v>0.06732492240542723</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.08464981930695632</v>
+        <v>-0.1254077231298754</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
@@ -2284,7 +2284,7 @@
         <v>0.06779732118811922</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06172665810409167</v>
+        <v>0.05357507733950786</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9475803835928353</v>
+        <v>0.968365337718633</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0976081757124632</v>
+        <v>0.09136178837015629</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0976081757124632</v>
+        <v>0.09136178837015629</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03537056275406315</v>
+        <v>-0.09150184053915233</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1374440427973116</v>
+        <v>0.1270032753031934</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1374440427973116</v>
+        <v>0.1270032753031934</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.01247650655453449</v>
+        <v>0.04135195306658596</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1795507460707608</v>
+        <v>0.174659546004692</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1795507460707608</v>
+        <v>0.174659546004692</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4055539306263216</v>
+        <v>-0.4158826652898435</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1534947298784935</v>
+        <v>-0.1660642607519296</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1106671991965087</v>
+        <v>0.1066745946289583</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1106671991965087</v>
+        <v>0.1066745946289583</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.07874399694149738</v>
+        <v>-0.1078991603896796</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08650012973102907</v>
+        <v>0.07845137925043882</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08650012973102907</v>
+        <v>0.07845137925043882</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03109339239796875</v>
+        <v>-0.0383827194978319</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5384275657753034</v>
+        <v>-0.6631892655686427</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2186518685691962</v>
+        <v>0.1793042734996289</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2186518685691962</v>
+        <v>0.1793042734996289</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5631655680372819</v>
+        <v>-0.5868630123183906</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4197524374981791</v>
+        <v>-0.4428554163596572</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04544291197167855</v>
+        <v>0.03862296942415755</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04544291197167855</v>
+        <v>0.03862296942415755</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3649084401309606</v>
+        <v>0.3639084662600452</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1139746484393356</v>
+        <v>-0.1205983056742146</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.501476559664817</v>
+        <v>-1.506791868839335</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1399351773480453</v>
+        <v>-0.2075181045738611</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1231319235437531</v>
+        <v>0.1030115251267388</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1231319235437531</v>
+        <v>0.1030115251267388</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7569397168591122</v>
+        <v>-0.8026581525455381</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09717205619843629</v>
+        <v>0.09037638782159269</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09717205619843629</v>
+        <v>0.09037638782159269</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4713908668617477</v>
+        <v>-0.455786018194908</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3371807617128011</v>
+        <v>0.3210289715684101</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04921262521961251</v>
+        <v>0.04478460622721853</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04921262521961251</v>
+        <v>0.04478460622721853</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.009606961113577905</v>
+        <v>-0.03366193566429354</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
@@ -4084,7 +4084,7 @@
         <v>0.0408515289132439</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03820651112979202</v>
+        <v>0.03339551621964889</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8462602482497803</v>
+        <v>-0.8531854729984851</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01872713295816157</v>
+        <v>-0.0449980684725198</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0910719621357256</v>
+        <v>0.08970817074422381</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0910719621357256</v>
+        <v>0.08970817074422381</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4771839307978255</v>
+        <v>-0.5085914998899366</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07328577667295567</v>
+        <v>0.06973916342451948</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07328577667295567</v>
+        <v>0.06973916342451948</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1093992020995611</v>
+        <v>0.10416139168702</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1081634496209517</v>
+        <v>0.1039205613335979</v>
       </c>
       <c r="J3" s="4">
-        <v>3.340910948098566</v>
+        <v>3.334210556567262</v>
       </c>
       <c r="K3" s="4">
         <v>90.40462018140607</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1766896935727388</v>
+        <v>0.1750162019697283</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1766896935727388</v>
+        <v>0.1750162019697283</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1753048599233669</v>
+        <v>0.1749265083888219</v>
       </c>
       <c r="K4" s="4">
         <v>87.2874149659864</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1057297623294504</v>
+        <v>0.1004194974354473</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1057297623294504</v>
+        <v>0.1004194974354473</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1035985767236474</v>
+        <v>0.09669999473135905</v>
       </c>
       <c r="K5" s="4">
         <v>88.02791950113378</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1562059893804407</v>
+        <v>0.1460056104867944</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1562059893804407</v>
+        <v>0.1460056104867944</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1709659077608982</v>
+        <v>0.1676824282158299</v>
       </c>
       <c r="K6" s="4">
         <v>90.6065759637187</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.0632020804033967</v>
+        <v>0.0597030949903553</v>
       </c>
       <c r="I7" s="4">
-        <v>0.0632020804033967</v>
+        <v>0.0597030949903553</v>
       </c>
       <c r="J7" s="4">
-        <v>0.06256690272757783</v>
+        <v>0.06101016029382551</v>
       </c>
       <c r="K7" s="4">
         <v>88.82653061224492</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.08377726185271246</v>
+        <v>0.08067441674223787</v>
       </c>
       <c r="I8" s="4">
-        <v>0.08377726185271246</v>
+        <v>0.08067441674223787</v>
       </c>
       <c r="J8" s="4">
-        <v>0.08310618196215616</v>
+        <v>0.08021634962781497</v>
       </c>
       <c r="K8" s="4">
         <v>89.19005102040816</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.2413469450194934</v>
+        <v>0.2291807631665874</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2413469450194934</v>
+        <v>0.2291807631665874</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2735281118474668</v>
+        <v>0.2546318947085889</v>
       </c>
       <c r="K9" s="4">
         <v>87.40433673469387</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.07100020764619557</v>
+        <v>0.06959344955341899</v>
       </c>
       <c r="I10" s="4">
-        <v>0.07042253894487512</v>
+        <v>0.06811866038580713</v>
       </c>
       <c r="J10" s="4">
-        <v>0.07284143392556704</v>
+        <v>0.07005860336846646</v>
       </c>
       <c r="K10" s="4">
         <v>83.74716553287961</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1019514894656189</v>
+        <v>0.09624889338564079</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1019514894656189</v>
+        <v>0.09624889338564079</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1023510620332965</v>
+        <v>0.09846829713056671</v>
       </c>
       <c r="K11" s="4">
         <v>88.10090702947848</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.07764009364271544</v>
+        <v>0.07533013964667939</v>
       </c>
       <c r="I12" s="4">
-        <v>0.07764009364271544</v>
+        <v>0.07533013964667939</v>
       </c>
       <c r="J12" s="4">
-        <v>0.07762861802033805</v>
+        <v>0.07473192497685092</v>
       </c>
       <c r="K12" s="4">
         <v>83.11295351473915</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1010090010107651</v>
+        <v>0.09228600646561368</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1010090010107651</v>
+        <v>0.09228600646561368</v>
       </c>
       <c r="J13" s="4">
-        <v>0.09988463780900891</v>
+        <v>0.09232378949030362</v>
       </c>
       <c r="K13" s="4">
         <v>88.70960884353747</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.04313151417636322</v>
+        <v>0.04085819999385622</v>
       </c>
       <c r="I14" s="4">
-        <v>0.04313151417636322</v>
+        <v>0.04085819999385622</v>
       </c>
       <c r="J14" s="4">
-        <v>0.04441280601185744</v>
+        <v>0.0431868548995968</v>
       </c>
       <c r="K14" s="4">
         <v>97.51700680272108</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.08996143135470207</v>
+        <v>0.08098940909008275</v>
       </c>
       <c r="I15" s="4">
-        <v>0.08996143135470207</v>
+        <v>0.08098940909008275</v>
       </c>
       <c r="J15" s="4">
-        <v>0.09302231922912395</v>
+        <v>0.08692720230527361</v>
       </c>
       <c r="K15" s="4">
         <v>82.56235827664416</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.0450582326595209</v>
+        <v>0.04358222632872291</v>
       </c>
       <c r="I16" s="4">
-        <v>0.04452773941416899</v>
+        <v>0.04154991067857609</v>
       </c>
       <c r="J16" s="4">
-        <v>0.04864793405145151</v>
+        <v>0.049373340645161</v>
       </c>
       <c r="K16" s="4">
         <v>94.71088435374081</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.06674440724303035</v>
+        <v>0.06510760569638435</v>
       </c>
       <c r="I17" s="4">
-        <v>0.06674440724303035</v>
+        <v>0.06510760569638435</v>
       </c>
       <c r="J17" s="4">
-        <v>0.06415040006809859</v>
+        <v>0.06640782643109482</v>
       </c>
       <c r="K17" s="4">
         <v>83.01587301587317</v>
@@ -6922,7 +6922,7 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>-26.34463893734019</v>
+        <v>-26.33097994140135</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -6981,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6525561554054303</v>
+        <v>-0.7146886323288966</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2000194566124091</v>
+        <v>0.1767428632314811</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2000194566124091</v>
+        <v>0.1767428632314811</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -7040,16 +7040,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.01039432655013435</v>
+        <v>0.04160482374621099</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1708976278674914</v>
+        <v>0.1535645777687096</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1715812397221488</v>
+        <v>0.1611814096628797</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -7222,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>1.165336178117982</v>
+        <v>1.141401913036016</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -7281,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3508730473935489</v>
+        <v>-0.3589163726513437</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
@@ -7340,16 +7340,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04014132690772459</v>
+        <v>-0.06006320425152928</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.149069531868847</v>
+        <v>0.1490695318688471</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.149069531868847</v>
+        <v>0.1490695318688471</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3267947794258682</v>
+        <v>-0.3301452415336334</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -7581,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1615394756515705</v>
+        <v>-0.206817800403562</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.0861797421906893</v>
+        <v>-0.2348019061032111</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2844086789669296</v>
+        <v>0.2561547400757336</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2844086789669296</v>
+        <v>0.2561547400757336</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -7822,16 +7822,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2326095438261914</v>
+        <v>-0.1985813809083594</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0698547761340168</v>
+        <v>0.06606763977332664</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0698547761340168</v>
+        <v>0.06606763977332664</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08759933142064842</v>
+        <v>-0.1493084288300938</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1522510021614609</v>
+        <v>0.131744723968151</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1522510021614609</v>
+        <v>0.131744723968151</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -7940,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05397739283586587</v>
+        <v>-0.04499201127917191</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1037064059317025</v>
+        <v>0.08467012780690419</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07581525472997461</v>
+        <v>-0.1359417296113438</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1305942975819186</v>
+        <v>0.1169696035275267</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1305942975819186</v>
+        <v>0.1169696035275267</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1246789919569596</v>
+        <v>-0.157935966463707</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07247836222072089</v>
+        <v>0.06453362547104034</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07247836222072089</v>
+        <v>0.06453362547104034</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
